--- a/Zinc/6. Statistical data analysis/Statistical_analyses_by_typology.xlsx
+++ b/Zinc/6. Statistical data analysis/Statistical_analyses_by_typology.xlsx
@@ -38474,7 +38474,7 @@
         <v>14.6563741934412</v>
       </c>
       <c r="C64" t="n">
-        <v>0.0000000000380703728972451</v>
+        <v>0.0000000000380703728972453</v>
       </c>
       <c r="D64" t="b">
         <v>0</v>

--- a/Zinc/6. Statistical data analysis/Statistical_analyses_by_typology.xlsx
+++ b/Zinc/6. Statistical data analysis/Statistical_analyses_by_typology.xlsx
@@ -41,16 +41,16 @@
     <t xml:space="preserve">BL_Ca_mol_kg</t>
   </si>
   <si>
-    <t xml:space="preserve">Pooled Water</t>
+    <t xml:space="preserve">Pooled</t>
   </si>
   <si>
-    <t xml:space="preserve">Non-Perennial Tribs</t>
+    <t xml:space="preserve">Non-Perennial</t>
   </si>
   <si>
-    <t xml:space="preserve">Perennial Tribs</t>
+    <t xml:space="preserve">Perennial</t>
   </si>
   <si>
-    <t xml:space="preserve">Developed Tribs</t>
+    <t xml:space="preserve">Developed Perennial</t>
   </si>
   <si>
     <t xml:space="preserve">Main Stem</t>
@@ -38474,7 +38474,7 @@
         <v>14.6563741934412</v>
       </c>
       <c r="C64" t="n">
-        <v>0.0000000000380703728972453</v>
+        <v>0.0000000000380703728972451</v>
       </c>
       <c r="D64" t="b">
         <v>0</v>
